--- a/photo_release_form_templates/035_student_media_release_form--photo_release_form_templates.xlsx
+++ b/photo_release_form_templates/035_student_media_release_form--photo_release_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -873,12 +873,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>student_media_release_form_parent_consent</t>
+          <t>student_media_release_form_parent_consent_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Parent or Guardian Consent</t>
+          <t>Student Media Release Form Parent Consent 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Student Media Release Form Consent Notes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -988,12 +988,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>student_media_release_form_consent_date</t>
+          <t>student_media_release_form_consent_date_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Consent Date</t>
+          <t>Student Media Release Form Consent Date 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>student_media_release_form_consent_time</t>
+          <t>student_media_release_form_consent_time_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Consent Time</t>
+          <t>Student Media Release Form Consent Time 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Student Media Release Form Educator Notes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'print_materials'}</t>
+          <t>print_materials</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Print Materials'}</t>
+          <t>Print Materials</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'websites'}</t>
+          <t>websites</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Websites'}</t>
+          <t>Websites</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1279,46 +1279,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>student_media_release_form_parent_consent_choices</t>
+          <t>student_media_release_form_parent_consent_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>student_media_release_form_parent_consent_choices</t>
+          <t>student_media_release_form_parent_consent_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
